--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
@@ -4203,7 +4203,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -4413,6 +4413,9 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4422,7 +4425,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4632,6 +4635,9 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>140000</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>142000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4674,7 +4680,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -4884,6 +4890,9 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4893,7 +4902,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>2000.0000000000002</c:v>
                 </c:pt>
@@ -5103,6 +5112,9 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>181233.60689088883</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>191635.63229330175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5145,7 +5157,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -5355,6 +5367,9 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5364,7 +5379,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5574,6 +5589,9 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>41233.606890888826</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>49635.632293301751</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5595,11 +5613,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="89142400"/>
-        <c:axId val="89143936"/>
+        <c:axId val="154671744"/>
+        <c:axId val="154699264"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="89142400"/>
+        <c:axId val="154671744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5642,14 +5660,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89143936"/>
+        <c:crossAx val="154699264"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="89143936"/>
+        <c:axId val="154699264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5700,7 +5718,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89142400"/>
+        <c:crossAx val="154671744"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6106,7 +6124,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB72"/>
+  <dimension ref="A1:AB73"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -8537,6 +8555,35 @@
       </c>
       <c r="I72" s="17">
         <v>41233.606890888826</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="12.75">
+      <c r="A73" s="14">
+        <v>46022</v>
+      </c>
+      <c r="B73" s="15">
+        <v>5.0477412109374997</v>
+      </c>
+      <c r="C73" s="16">
+        <v>2000</v>
+      </c>
+      <c r="D73" s="17">
+        <v>396.21682578860788</v>
+      </c>
+      <c r="E73" s="17">
+        <v>37964.630967622434</v>
+      </c>
+      <c r="F73" s="17">
+        <v>191635.63229330175</v>
+      </c>
+      <c r="G73" s="17">
+        <v>142000</v>
+      </c>
+      <c r="H73" s="17">
+        <v>191635.63229330175</v>
+      </c>
+      <c r="I73" s="17">
+        <v>49635.632293301751</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="906">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="924">
   <si>
     <t>PE</t>
   </si>
@@ -3631,6 +3631,78 @@
   </si>
   <si>
     <t xml:space="preserve">2025/11/26
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/5
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/6
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/7
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/8
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/9
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/12
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/13
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/14
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/15
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/16
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/19
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/20
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/21
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/22
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/23
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/26
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/27
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/28
 </t>
   </si>
 </sst>
@@ -5613,11 +5685,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="154671744"/>
-        <c:axId val="154699264"/>
+        <c:axId val="652698368"/>
+        <c:axId val="652700672"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="154671744"/>
+        <c:axId val="652698368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5660,14 +5732,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="154699264"/>
+        <c:crossAx val="652700672"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="154699264"/>
+        <c:axId val="652700672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5718,7 +5790,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="154671744"/>
+        <c:crossAx val="652698368"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8599,7 +8671,7 @@
   <sheetPr codeName="Sheet4">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1154"/>
+  <dimension ref="A1:D1173"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="18"/>
@@ -26690,7 +26762,7 @@
     </row>
     <row r="1132" spans="1:4">
       <c r="A1132" s="18">
-        <f t="shared" ref="A1132:A1154" si="7">A1131+1</f>
+        <f t="shared" ref="A1132:A1173" si="7">A1131+1</f>
         <v>1130</v>
       </c>
       <c r="B1132" s="30">
@@ -27054,6 +27126,310 @@
       <c r="D1154" s="18">
         <f>SUM(C$3:C1154)/A1154</f>
         <v>25.866548769817285</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:4">
+      <c r="A1155" s="18">
+        <f t="shared" si="7"/>
+        <v>1153</v>
+      </c>
+      <c r="B1155" s="30" t="s">
+        <v>906</v>
+      </c>
+      <c r="C1155" s="31">
+        <v>32.090000150000002</v>
+      </c>
+      <c r="D1155" s="18">
+        <f>SUM(C$3:C1155)/A1155</f>
+        <v>25.871946385931928</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:4">
+      <c r="A1156" s="18">
+        <f t="shared" si="7"/>
+        <v>1154</v>
+      </c>
+      <c r="B1156" s="30" t="s">
+        <v>907</v>
+      </c>
+      <c r="C1156" s="31">
+        <v>32.189998629999998</v>
+      </c>
+      <c r="D1156" s="18">
+        <f>SUM(C$3:C1156)/A1156</f>
+        <v>25.877421301221418</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:4">
+      <c r="A1157" s="18">
+        <f t="shared" si="7"/>
+        <v>1155</v>
+      </c>
+      <c r="B1157" s="30" t="s">
+        <v>908</v>
+      </c>
+      <c r="C1157" s="31">
+        <v>31.979999540000001</v>
+      </c>
+      <c r="D1157" s="18">
+        <f>SUM(C$3:C1157)/A1157</f>
+        <v>25.882704918744167</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:4">
+      <c r="A1158" s="18">
+        <f t="shared" si="7"/>
+        <v>1156</v>
+      </c>
+      <c r="B1158" s="30" t="s">
+        <v>909</v>
+      </c>
+      <c r="C1158" s="31">
+        <v>32.33000183</v>
+      </c>
+      <c r="D1158" s="18">
+        <f>SUM(C$3:C1158)/A1158</f>
+        <v>25.88828216520719</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:4">
+      <c r="A1159" s="18">
+        <f t="shared" si="7"/>
+        <v>1157</v>
+      </c>
+      <c r="B1159" s="30" t="s">
+        <v>910</v>
+      </c>
+      <c r="C1159" s="31">
+        <v>32.66999817</v>
+      </c>
+      <c r="D1159" s="18">
+        <f>SUM(C$3:C1159)/A1159</f>
+        <v>25.894143631071316</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:4">
+      <c r="A1160" s="18">
+        <f t="shared" si="7"/>
+        <v>1158</v>
+      </c>
+      <c r="B1160" s="30" t="s">
+        <v>911</v>
+      </c>
+      <c r="C1160" s="31">
+        <v>32.02999878</v>
+      </c>
+      <c r="D1160" s="18">
+        <f>SUM(C$3:C1160)/A1160</f>
+        <v>25.899442297003034</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:4">
+      <c r="A1161" s="18">
+        <f t="shared" si="7"/>
+        <v>1159</v>
+      </c>
+      <c r="B1161" s="30" t="s">
+        <v>912</v>
+      </c>
+      <c r="C1161" s="31">
+        <v>32.090000150000002</v>
+      </c>
+      <c r="D1161" s="18">
+        <f>SUM(C$3:C1161)/A1161</f>
+        <v>25.904783589369728</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:4">
+      <c r="A1162" s="18">
+        <f t="shared" si="7"/>
+        <v>1160</v>
+      </c>
+      <c r="B1162" s="30" t="s">
+        <v>913</v>
+      </c>
+      <c r="C1162" s="31">
+        <v>32.299999239999998</v>
+      </c>
+      <c r="D1162" s="18">
+        <f>SUM(C$3:C1162)/A1162</f>
+        <v>25.910296706309925</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:4">
+      <c r="A1163" s="18">
+        <f t="shared" si="7"/>
+        <v>1161</v>
+      </c>
+      <c r="B1163" s="30" t="s">
+        <v>914</v>
+      </c>
+      <c r="C1163" s="31">
+        <v>32.520000459999999</v>
+      </c>
+      <c r="D1163" s="18">
+        <f>SUM(C$3:C1163)/A1163</f>
+        <v>25.915989818931539</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:4">
+      <c r="A1164" s="18">
+        <f t="shared" si="7"/>
+        <v>1162</v>
+      </c>
+      <c r="B1164" s="30" t="s">
+        <v>915</v>
+      </c>
+      <c r="C1164" s="31">
+        <v>32.47000122</v>
+      </c>
+      <c r="D1164" s="18">
+        <f>SUM(C$3:C1164)/A1164</f>
+        <v>25.921630104130394</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:4">
+      <c r="A1165" s="18">
+        <f t="shared" si="7"/>
+        <v>1163</v>
+      </c>
+      <c r="B1165" s="30" t="s">
+        <v>916</v>
+      </c>
+      <c r="C1165" s="31">
+        <v>31.969999309999999</v>
+      </c>
+      <c r="D1165" s="18">
+        <f>SUM(C$3:C1165)/A1165</f>
+        <v>25.92683076552839</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:4">
+      <c r="A1166" s="18">
+        <f t="shared" si="7"/>
+        <v>1164</v>
+      </c>
+      <c r="B1166" s="30" t="s">
+        <v>917</v>
+      </c>
+      <c r="C1166" s="31">
+        <v>32.180000309999997</v>
+      </c>
+      <c r="D1166" s="18">
+        <f>SUM(C$3:C1166)/A1166</f>
+        <v>25.932202904312298</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:4">
+      <c r="A1167" s="18">
+        <f t="shared" si="7"/>
+        <v>1165</v>
+      </c>
+      <c r="B1167" s="30" t="s">
+        <v>918</v>
+      </c>
+      <c r="C1167" s="31">
+        <v>32.25</v>
+      </c>
+      <c r="D1167" s="18">
+        <f>SUM(C$3:C1167)/A1167</f>
+        <v>25.937625906111172</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:4">
+      <c r="A1168" s="18">
+        <f t="shared" si="7"/>
+        <v>1166</v>
+      </c>
+      <c r="B1168" s="30" t="s">
+        <v>919</v>
+      </c>
+      <c r="C1168" s="31">
+        <v>32.38999939</v>
+      </c>
+      <c r="D1168" s="18">
+        <f>SUM(C$3:C1168)/A1168</f>
+        <v>25.943159674107648</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:4">
+      <c r="A1169" s="18">
+        <f t="shared" si="7"/>
+        <v>1167</v>
+      </c>
+      <c r="B1169" s="30" t="s">
+        <v>920</v>
+      </c>
+      <c r="C1169" s="31">
+        <v>31.93000031</v>
+      </c>
+      <c r="D1169" s="18">
+        <f>SUM(C$3:C1169)/A1169</f>
+        <v>25.948289786049287</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:4">
+      <c r="A1170" s="18">
+        <f t="shared" si="7"/>
+        <v>1168</v>
+      </c>
+      <c r="B1170" s="30" t="s">
+        <v>921</v>
+      </c>
+      <c r="C1170" s="31">
+        <v>32.02999878</v>
+      </c>
+      <c r="D1170" s="18">
+        <f>SUM(C$3:C1170)/A1170</f>
+        <v>25.953496728681092</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:4">
+      <c r="A1171" s="18">
+        <f t="shared" si="7"/>
+        <v>1169</v>
+      </c>
+      <c r="B1171" s="30" t="s">
+        <v>922</v>
+      </c>
+      <c r="C1171" s="31">
+        <v>31.959999079999999</v>
+      </c>
+      <c r="D1171" s="18">
+        <f>SUM(C$3:C1171)/A1171</f>
+        <v>25.958634882959384</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:4">
+      <c r="A1172" s="18">
+        <f t="shared" si="7"/>
+        <v>1170</v>
+      </c>
+      <c r="B1172" s="30" t="s">
+        <v>923</v>
+      </c>
+      <c r="C1172" s="31">
+        <v>31.540000920000001</v>
+      </c>
+      <c r="D1172" s="18">
+        <f>SUM(C$3:C1172)/A1172</f>
+        <v>25.963405281281638</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:4">
+      <c r="A1173" s="18">
+        <f t="shared" si="7"/>
+        <v>1171</v>
+      </c>
+      <c r="B1173" s="30">
+        <v>46051</v>
+      </c>
+      <c r="C1173" s="31">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D1173" s="18">
+        <f>SUM(C$3:C1173)/A1173</f>
+        <v>25.968312705533322</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
@@ -4275,7 +4275,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -4488,6 +4488,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4497,7 +4500,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4710,6 +4713,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>142000</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>144000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4752,7 +4758,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -4965,6 +4971,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4974,7 +4983,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>2000.0000000000002</c:v>
                 </c:pt>
@@ -5187,6 +5196,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>191635.63229330175</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>198435.56287226095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5229,7 +5241,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -5442,6 +5454,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5451,7 +5466,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5664,6 +5679,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>49635.632293301751</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>54435.562872260954</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5685,11 +5703,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="88178688"/>
-        <c:axId val="88180224"/>
+        <c:axId val="409097344"/>
+        <c:axId val="493123840"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="88178688"/>
+        <c:axId val="409097344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5732,14 +5750,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88180224"/>
+        <c:crossAx val="493123840"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="88180224"/>
+        <c:axId val="493123840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5790,7 +5808,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88178688"/>
+        <c:crossAx val="409097344"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6196,7 +6214,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB73"/>
+  <dimension ref="A1:AB74"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -8656,6 +8674,35 @@
       </c>
       <c r="I73" s="17">
         <v>49635.632293301751</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="12.75">
+      <c r="A74" s="14">
+        <v>46052</v>
+      </c>
+      <c r="B74" s="15">
+        <v>5.1741728515625001</v>
+      </c>
+      <c r="C74" s="16">
+        <v>2000</v>
+      </c>
+      <c r="D74" s="17">
+        <v>386.53521198002471</v>
+      </c>
+      <c r="E74" s="17">
+        <v>38351.166179602456</v>
+      </c>
+      <c r="F74" s="17">
+        <v>198435.56287226095</v>
+      </c>
+      <c r="G74" s="17">
+        <v>144000</v>
+      </c>
+      <c r="H74" s="17">
+        <v>198435.56287226095</v>
+      </c>
+      <c r="I74" s="17">
+        <v>54435.562872260954</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="924">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="936">
   <si>
     <t>PE</t>
   </si>
@@ -3703,6 +3703,54 @@
   </si>
   <si>
     <t xml:space="preserve">2026/1/28
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/2
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/3
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/4
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/5
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/6
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/9
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/10
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/11
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/12
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/13
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/24
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/25
 </t>
   </si>
 </sst>
@@ -4275,7 +4323,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -4488,6 +4536,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4497,7 +4548,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4710,6 +4761,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>142000</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>144000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4752,7 +4806,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -4965,6 +5019,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4974,7 +5031,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>2000.0000000000002</c:v>
                 </c:pt>
@@ -5187,6 +5244,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>191635.63229330175</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>198435.56287226095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5229,7 +5289,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -5442,6 +5502,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5451,7 +5514,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5664,6 +5727,9 @@
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>49635.632293301751</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>54435.562872260954</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5685,11 +5751,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="88178688"/>
-        <c:axId val="88180224"/>
+        <c:axId val="689598464"/>
+        <c:axId val="689601152"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="88178688"/>
+        <c:axId val="689598464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5732,14 +5798,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88180224"/>
+        <c:crossAx val="689601152"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="88180224"/>
+        <c:axId val="689601152"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5790,7 +5856,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88178688"/>
+        <c:crossAx val="689598464"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6196,7 +6262,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB73"/>
+  <dimension ref="A1:AB74"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -8658,6 +8724,35 @@
         <v>49635.632293301751</v>
       </c>
     </row>
+    <row r="74" spans="1:9" ht="12.75">
+      <c r="A74" s="14">
+        <v>46052</v>
+      </c>
+      <c r="B74" s="15">
+        <v>5.1741728515625001</v>
+      </c>
+      <c r="C74" s="16">
+        <v>2000</v>
+      </c>
+      <c r="D74" s="17">
+        <v>386.53521198002471</v>
+      </c>
+      <c r="E74" s="17">
+        <v>38351.166179602456</v>
+      </c>
+      <c r="F74" s="17">
+        <v>198435.56287226095</v>
+      </c>
+      <c r="G74" s="17">
+        <v>144000</v>
+      </c>
+      <c r="H74" s="17">
+        <v>198435.56287226095</v>
+      </c>
+      <c r="I74" s="17">
+        <v>54435.562872260954</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8671,7 +8766,7 @@
   <sheetPr codeName="Sheet4">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1174"/>
+  <dimension ref="A1:D1187"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="18"/>
@@ -26762,7 +26857,7 @@
     </row>
     <row r="1132" spans="1:4">
       <c r="A1132" s="18">
-        <f t="shared" ref="A1132:A1174" si="7">A1131+1</f>
+        <f t="shared" ref="A1132:A1187" si="7">A1131+1</f>
         <v>1130</v>
       </c>
       <c r="B1132" s="30">
@@ -27446,6 +27541,214 @@
       <c r="D1174" s="18">
         <f>SUM(C$3:C1174)/A1174</f>
         <v>25.973356806597167</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:4">
+      <c r="A1175" s="18">
+        <f t="shared" si="7"/>
+        <v>1173</v>
+      </c>
+      <c r="B1175" s="30" t="s">
+        <v>924</v>
+      </c>
+      <c r="C1175" s="31">
+        <v>30.950000760000002</v>
+      </c>
+      <c r="D1175" s="18">
+        <f>SUM(C$3:C1175)/A1175</f>
+        <v>25.977599469814049</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:4">
+      <c r="A1176" s="18">
+        <f t="shared" si="7"/>
+        <v>1174</v>
+      </c>
+      <c r="B1176" s="30" t="s">
+        <v>925</v>
+      </c>
+      <c r="C1176" s="31">
+        <v>31.409999849999998</v>
+      </c>
+      <c r="D1176" s="18">
+        <f>SUM(C$3:C1176)/A1176</f>
+        <v>25.982226727378087</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:4">
+      <c r="A1177" s="18">
+        <f t="shared" si="7"/>
+        <v>1175</v>
+      </c>
+      <c r="B1177" s="30" t="s">
+        <v>926</v>
+      </c>
+      <c r="C1177" s="31">
+        <v>31.579999919999999</v>
+      </c>
+      <c r="D1177" s="18">
+        <f>SUM(C$3:C1177)/A1177</f>
+        <v>25.986990789669679</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:4">
+      <c r="A1178" s="18">
+        <f t="shared" si="7"/>
+        <v>1176</v>
+      </c>
+      <c r="B1178" s="30" t="s">
+        <v>927</v>
+      </c>
+      <c r="C1178" s="31">
+        <v>31.229999540000001</v>
+      </c>
+      <c r="D1178" s="18">
+        <f>SUM(C$3:C1178)/A1178</f>
+        <v>25.991449130443769</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:4">
+      <c r="A1179" s="18">
+        <f t="shared" si="7"/>
+        <v>1177</v>
+      </c>
+      <c r="B1179" s="30" t="s">
+        <v>928</v>
+      </c>
+      <c r="C1179" s="31">
+        <v>31.219999309999999</v>
+      </c>
+      <c r="D1179" s="18">
+        <f>SUM(C$3:C1179)/A1179</f>
+        <v>25.995891399075511</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:4">
+      <c r="A1180" s="18">
+        <f t="shared" si="7"/>
+        <v>1178</v>
+      </c>
+      <c r="B1180" s="30" t="s">
+        <v>929</v>
+      </c>
+      <c r="C1180" s="31">
+        <v>31.729999540000001</v>
+      </c>
+      <c r="D1180" s="18">
+        <f>SUM(C$3:C1180)/A1180</f>
+        <v>26.000759063032152</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:4">
+      <c r="A1181" s="18">
+        <f t="shared" si="7"/>
+        <v>1179</v>
+      </c>
+      <c r="B1181" s="30" t="s">
+        <v>930</v>
+      </c>
+      <c r="C1181" s="31">
+        <v>31.760000229999999</v>
+      </c>
+      <c r="D1181" s="18">
+        <f>SUM(C$3:C1181)/A1181</f>
+        <v>26.005643915591069</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:4">
+      <c r="A1182" s="18">
+        <f t="shared" si="7"/>
+        <v>1180</v>
+      </c>
+      <c r="B1182" s="30" t="s">
+        <v>931</v>
+      </c>
+      <c r="C1182" s="31">
+        <v>31.590000150000002</v>
+      </c>
+      <c r="D1182" s="18">
+        <f>SUM(C$3:C1182)/A1182</f>
+        <v>26.010376420874469</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:4">
+      <c r="A1183" s="18">
+        <f t="shared" si="7"/>
+        <v>1181</v>
+      </c>
+      <c r="B1183" s="30" t="s">
+        <v>932</v>
+      </c>
+      <c r="C1183" s="31">
+        <v>32</v>
+      </c>
+      <c r="D1183" s="18">
+        <f>SUM(C$3:C1183)/A1183</f>
+        <v>26.015448075048155</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:4">
+      <c r="A1184" s="18">
+        <f t="shared" si="7"/>
+        <v>1182</v>
+      </c>
+      <c r="B1184" s="30" t="s">
+        <v>933</v>
+      </c>
+      <c r="C1184" s="31">
+        <v>31.590000150000002</v>
+      </c>
+      <c r="D1184" s="18">
+        <f>SUM(C$3:C1184)/A1184</f>
+        <v>26.020164278157253</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:4">
+      <c r="A1185" s="18">
+        <f t="shared" si="7"/>
+        <v>1183</v>
+      </c>
+      <c r="B1185" s="30" t="s">
+        <v>934</v>
+      </c>
+      <c r="C1185" s="31">
+        <v>31.829999919999999</v>
+      </c>
+      <c r="D1185" s="18">
+        <f>SUM(C$3:C1185)/A1185</f>
+        <v>26.025075381827449</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:4">
+      <c r="A1186" s="18">
+        <f t="shared" si="7"/>
+        <v>1184</v>
+      </c>
+      <c r="B1186" s="30" t="s">
+        <v>935</v>
+      </c>
+      <c r="C1186" s="31">
+        <v>32.090000150000002</v>
+      </c>
+      <c r="D1186" s="18">
+        <f>SUM(C$3:C1186)/A1186</f>
+        <v>26.030197784503272</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:4">
+      <c r="A1187" s="18">
+        <f t="shared" si="7"/>
+        <v>1185</v>
+      </c>
+      <c r="B1187" s="30">
+        <v>46079</v>
+      </c>
+      <c r="C1187" s="31">
+        <v>31.920000080000001</v>
+      </c>
+      <c r="D1187" s="18">
+        <f>SUM(C$3:C1187)/A1187</f>
+        <v>26.03516808179905</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
@@ -5751,11 +5751,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="689598464"/>
-        <c:axId val="689601152"/>
+        <c:axId val="383488768"/>
+        <c:axId val="383490304"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="689598464"/>
+        <c:axId val="383488768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5798,14 +5798,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="689601152"/>
+        <c:crossAx val="383490304"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="689601152"/>
+        <c:axId val="383490304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5856,7 +5856,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="689598464"/>
+        <c:crossAx val="383488768"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8766,7 +8766,7 @@
   <sheetPr codeName="Sheet4">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1187"/>
+  <dimension ref="A1:D1188"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="18"/>
@@ -26857,7 +26857,7 @@
     </row>
     <row r="1132" spans="1:4">
       <c r="A1132" s="18">
-        <f t="shared" ref="A1132:A1187" si="7">A1131+1</f>
+        <f t="shared" ref="A1132:A1188" si="7">A1131+1</f>
         <v>1130</v>
       </c>
       <c r="B1132" s="30">
@@ -27749,6 +27749,22 @@
       <c r="D1187" s="18">
         <f>SUM(C$3:C1187)/A1187</f>
         <v>26.03516808179905</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:4">
+      <c r="A1188" s="18">
+        <f t="shared" si="7"/>
+        <v>1186</v>
+      </c>
+      <c r="B1188" s="30">
+        <v>46080</v>
+      </c>
+      <c r="C1188" s="31">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D1188" s="18">
+        <f>SUM(C$3:C1188)/A1188</f>
+        <v>26.039818023753689</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
@@ -4323,7 +4323,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -4539,6 +4539,9 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4548,7 +4551,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4764,6 +4767,9 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>144000</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>146000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4806,7 +4812,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -5022,6 +5028,9 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5031,7 +5040,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>2000.0000000000002</c:v>
                 </c:pt>
@@ -5247,6 +5256,9 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>198435.56287226095</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>198359.00077810945</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5289,7 +5301,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -5505,6 +5517,9 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5514,7 +5529,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5730,6 +5745,9 @@
                 </c:pt>
                 <c:pt idx="71">
                   <c:v>54435.562872260954</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>52359.000778109446</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5751,11 +5769,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="383488768"/>
-        <c:axId val="383490304"/>
+        <c:axId val="97854208"/>
+        <c:axId val="97856128"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="383488768"/>
+        <c:axId val="97854208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5798,14 +5816,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="383490304"/>
+        <c:crossAx val="97856128"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="383490304"/>
+        <c:axId val="97856128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5856,7 +5874,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="383488768"/>
+        <c:crossAx val="97854208"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6262,7 +6280,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB74"/>
+  <dimension ref="A1:AB75"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -8751,6 +8769,35 @@
       </c>
       <c r="I74" s="17">
         <v>54435.562872260954</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="12.75">
+      <c r="A75" s="14">
+        <v>46080</v>
+      </c>
+      <c r="B75" s="15">
+        <v>5.1200268554687502</v>
+      </c>
+      <c r="C75" s="16">
+        <v>2000</v>
+      </c>
+      <c r="D75" s="17">
+        <v>390.62295110108272</v>
+      </c>
+      <c r="E75" s="17">
+        <v>38741.789130703539</v>
+      </c>
+      <c r="F75" s="17">
+        <v>198359.00077810945</v>
+      </c>
+      <c r="G75" s="17">
+        <v>146000</v>
+      </c>
+      <c r="H75" s="17">
+        <v>198359.00077810945</v>
+      </c>
+      <c r="I75" s="17">
+        <v>52359.000778109446</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="936">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="956">
   <si>
     <t>PE</t>
   </si>
@@ -3751,6 +3751,86 @@
   </si>
   <si>
     <t xml:space="preserve">2026/2/25
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/2
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/3
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/4
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/5
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/6
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/9
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/10
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/11
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/12
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/13
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/16
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/17
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/18
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/19
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/20
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/23
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/24
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/25
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/26
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/27
 </t>
   </si>
 </sst>
@@ -5769,11 +5849,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="97854208"/>
-        <c:axId val="97856128"/>
+        <c:axId val="518796416"/>
+        <c:axId val="518832512"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="97854208"/>
+        <c:axId val="518796416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5816,14 +5896,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97856128"/>
+        <c:crossAx val="518832512"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="97856128"/>
+        <c:axId val="518832512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5874,7 +5954,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97854208"/>
+        <c:crossAx val="518796416"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8813,7 +8893,7 @@
   <sheetPr codeName="Sheet4">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1188"/>
+  <dimension ref="A1:D1209"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="18"/>
@@ -26904,7 +26984,7 @@
     </row>
     <row r="1132" spans="1:4">
       <c r="A1132" s="18">
-        <f t="shared" ref="A1132:A1188" si="7">A1131+1</f>
+        <f t="shared" ref="A1132:A1209" si="7">A1131+1</f>
         <v>1130</v>
       </c>
       <c r="B1132" s="30">
@@ -27812,6 +27892,342 @@
       <c r="D1188" s="18">
         <f>SUM(C$3:C1188)/A1188</f>
         <v>26.039818023753689</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:4">
+      <c r="A1189" s="18">
+        <f t="shared" si="7"/>
+        <v>1187</v>
+      </c>
+      <c r="B1189" s="30" t="s">
+        <v>936</v>
+      </c>
+      <c r="C1189" s="31">
+        <v>31.690000529999999</v>
+      </c>
+      <c r="D1189" s="18">
+        <f>SUM(C$3:C1189)/A1189</f>
+        <v>26.044578076412702</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:4">
+      <c r="A1190" s="18">
+        <f t="shared" si="7"/>
+        <v>1188</v>
+      </c>
+      <c r="B1190" s="30" t="s">
+        <v>937</v>
+      </c>
+      <c r="C1190" s="31">
+        <v>30.899999619999999</v>
+      </c>
+      <c r="D1190" s="18">
+        <f>SUM(C$3:C1190)/A1190</f>
+        <v>26.048665131584073</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:4">
+      <c r="A1191" s="18">
+        <f t="shared" si="7"/>
+        <v>1189</v>
+      </c>
+      <c r="B1191" s="30" t="s">
+        <v>938</v>
+      </c>
+      <c r="C1191" s="31">
+        <v>30.629999160000001</v>
+      </c>
+      <c r="D1191" s="18">
+        <f>SUM(C$3:C1191)/A1191</f>
+        <v>26.052518230009987</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:4">
+      <c r="A1192" s="18">
+        <f t="shared" si="7"/>
+        <v>1190</v>
+      </c>
+      <c r="B1192" s="30" t="s">
+        <v>939</v>
+      </c>
+      <c r="C1192" s="31">
+        <v>31.059999470000001</v>
+      </c>
+      <c r="D1192" s="18">
+        <f>SUM(C$3:C1192)/A1192</f>
+        <v>26.05672619743855</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:4">
+      <c r="A1193" s="18">
+        <f t="shared" si="7"/>
+        <v>1191</v>
+      </c>
+      <c r="B1193" s="30" t="s">
+        <v>940</v>
+      </c>
+      <c r="C1193" s="31">
+        <v>31.170000080000001</v>
+      </c>
+      <c r="D1193" s="18">
+        <f>SUM(C$3:C1193)/A1193</f>
+        <v>26.061019458465051</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:4">
+      <c r="A1194" s="18">
+        <f t="shared" si="7"/>
+        <v>1192</v>
+      </c>
+      <c r="B1194" s="30" t="s">
+        <v>941</v>
+      </c>
+      <c r="C1194" s="31">
+        <v>30.950000760000002</v>
+      </c>
+      <c r="D1194" s="18">
+        <f>SUM(C$3:C1194)/A1194</f>
+        <v>26.065120952845533</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:4">
+      <c r="A1195" s="18">
+        <f t="shared" si="7"/>
+        <v>1193</v>
+      </c>
+      <c r="B1195" s="30" t="s">
+        <v>942</v>
+      </c>
+      <c r="C1195" s="31">
+        <v>30.950000760000002</v>
+      </c>
+      <c r="D1195" s="18">
+        <f>SUM(C$3:C1195)/A1195</f>
+        <v>26.069215571292435</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:4">
+      <c r="A1196" s="18">
+        <f t="shared" si="7"/>
+        <v>1194</v>
+      </c>
+      <c r="B1196" s="30" t="s">
+        <v>943</v>
+      </c>
+      <c r="C1196" s="31">
+        <v>32.36000061</v>
+      </c>
+      <c r="D1196" s="18">
+        <f>SUM(C$3:C1196)/A1196</f>
+        <v>26.074484235478955</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:4">
+      <c r="A1197" s="18">
+        <f t="shared" si="7"/>
+        <v>1195</v>
+      </c>
+      <c r="B1197" s="30" t="s">
+        <v>944</v>
+      </c>
+      <c r="C1197" s="31">
+        <v>32.150001529999997</v>
+      </c>
+      <c r="D1197" s="18">
+        <f>SUM(C$3:C1197)/A1197</f>
+        <v>26.079568350369769</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:4">
+      <c r="A1198" s="18">
+        <f t="shared" si="7"/>
+        <v>1196</v>
+      </c>
+      <c r="B1198" s="30" t="s">
+        <v>945</v>
+      </c>
+      <c r="C1198" s="31">
+        <v>31.950000760000002</v>
+      </c>
+      <c r="D1198" s="18">
+        <f>SUM(C$3:C1198)/A1198</f>
+        <v>26.084476738672137</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:4">
+      <c r="A1199" s="18">
+        <f t="shared" si="7"/>
+        <v>1197</v>
+      </c>
+      <c r="B1199" s="30" t="s">
+        <v>946</v>
+      </c>
+      <c r="C1199" s="31">
+        <v>32.25</v>
+      </c>
+      <c r="D1199" s="18">
+        <f>SUM(C$3:C1199)/A1199</f>
+        <v>26.089627551755953</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:4">
+      <c r="A1200" s="18">
+        <f t="shared" si="7"/>
+        <v>1198</v>
+      </c>
+      <c r="B1200" s="30" t="s">
+        <v>947</v>
+      </c>
+      <c r="C1200" s="31">
+        <v>31.719999309999999</v>
+      </c>
+      <c r="D1200" s="18">
+        <f>SUM(C$3:C1200)/A1200</f>
+        <v>26.094327361236957</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:4">
+      <c r="A1201" s="18">
+        <f t="shared" si="7"/>
+        <v>1199</v>
+      </c>
+      <c r="B1201" s="30" t="s">
+        <v>948</v>
+      </c>
+      <c r="C1201" s="31">
+        <v>32.060001370000002</v>
+      </c>
+      <c r="D1201" s="18">
+        <f>SUM(C$3:C1201)/A1201</f>
+        <v>26.09930290252867</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:4">
+      <c r="A1202" s="18">
+        <f t="shared" si="7"/>
+        <v>1200</v>
+      </c>
+      <c r="B1202" s="30" t="s">
+        <v>949</v>
+      </c>
+      <c r="C1202" s="31">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D1202" s="18">
+        <f>SUM(C$3:C1202)/A1202</f>
+        <v>26.103845149476562</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:4">
+      <c r="A1203" s="18">
+        <f t="shared" si="7"/>
+        <v>1201</v>
+      </c>
+      <c r="B1203" s="30" t="s">
+        <v>950</v>
+      </c>
+      <c r="C1203" s="31">
+        <v>31.729999540000001</v>
+      </c>
+      <c r="D1203" s="18">
+        <f>SUM(C$3:C1203)/A1203</f>
+        <v>26.108529707670169</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:4">
+      <c r="A1204" s="18">
+        <f t="shared" si="7"/>
+        <v>1202</v>
+      </c>
+      <c r="B1204" s="30" t="s">
+        <v>951</v>
+      </c>
+      <c r="C1204" s="31">
+        <v>30.75</v>
+      </c>
+      <c r="D1204" s="18">
+        <f>SUM(C$3:C1204)/A1204</f>
+        <v>26.112391163820195</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:4">
+      <c r="A1205" s="18">
+        <f t="shared" si="7"/>
+        <v>1203</v>
+      </c>
+      <c r="B1205" s="30" t="s">
+        <v>952</v>
+      </c>
+      <c r="C1205" s="31">
+        <v>30.870000839999999</v>
+      </c>
+      <c r="D1205" s="18">
+        <f>SUM(C$3:C1205)/A1205</f>
+        <v>26.116345951580943</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:4">
+      <c r="A1206" s="18">
+        <f t="shared" si="7"/>
+        <v>1204</v>
+      </c>
+      <c r="B1206" s="30" t="s">
+        <v>953</v>
+      </c>
+      <c r="C1206" s="31">
+        <v>31.38999939</v>
+      </c>
+      <c r="D1206" s="18">
+        <f>SUM(C$3:C1206)/A1206</f>
+        <v>26.120726062410196</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:4">
+      <c r="A1207" s="18">
+        <f t="shared" si="7"/>
+        <v>1205</v>
+      </c>
+      <c r="B1207" s="30" t="s">
+        <v>954</v>
+      </c>
+      <c r="C1207" s="31">
+        <v>30.969999309999999</v>
+      </c>
+      <c r="D1207" s="18">
+        <f>SUM(C$3:C1207)/A1207</f>
+        <v>26.124750355561723</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:4">
+      <c r="A1208" s="18">
+        <f t="shared" si="7"/>
+        <v>1206</v>
+      </c>
+      <c r="B1208" s="30" t="s">
+        <v>955</v>
+      </c>
+      <c r="C1208" s="31">
+        <v>31.299999239999998</v>
+      </c>
+      <c r="D1208" s="18">
+        <f>SUM(C$3:C1208)/A1208</f>
+        <v>26.129041606709681</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:4">
+      <c r="A1209" s="18">
+        <f t="shared" si="7"/>
+        <v>1207</v>
+      </c>
+      <c r="B1209" s="30">
+        <v>46111</v>
+      </c>
+      <c r="C1209" s="31">
+        <v>31.299999239999998</v>
+      </c>
+      <c r="D1209" s="18">
+        <f>SUM(C$3:C1209)/A1209</f>
+        <v>26.133325747250932</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
@@ -5849,11 +5849,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="518796416"/>
-        <c:axId val="518832512"/>
+        <c:axId val="329935488"/>
+        <c:axId val="346255744"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="518796416"/>
+        <c:axId val="329935488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5896,14 +5896,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="518832512"/>
+        <c:crossAx val="346255744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="518832512"/>
+        <c:axId val="346255744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5954,7 +5954,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="518796416"/>
+        <c:crossAx val="329935488"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8893,7 +8893,7 @@
   <sheetPr codeName="Sheet4">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1209"/>
+  <dimension ref="A1:D1210"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="18"/>
@@ -26984,7 +26984,7 @@
     </row>
     <row r="1132" spans="1:4">
       <c r="A1132" s="18">
-        <f t="shared" ref="A1132:A1209" si="7">A1131+1</f>
+        <f t="shared" ref="A1132:A1210" si="7">A1131+1</f>
         <v>1130</v>
       </c>
       <c r="B1132" s="30">
@@ -28228,6 +28228,22 @@
       <c r="D1209" s="18">
         <f>SUM(C$3:C1209)/A1209</f>
         <v>26.133325747250932</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:4">
+      <c r="A1210" s="18">
+        <f t="shared" si="7"/>
+        <v>1208</v>
+      </c>
+      <c r="B1210" s="30">
+        <v>46112</v>
+      </c>
+      <c r="C1210" s="31">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D1210" s="18">
+        <f>SUM(C$3:C1210)/A1210</f>
+        <v>26.136981933917117</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
@@ -4403,7 +4403,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -4622,6 +4622,9 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4631,7 +4634,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4850,6 +4853,9 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>146000</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>148000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4892,7 +4898,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -5111,6 +5117,9 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5120,7 +5129,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>2000.0000000000002</c:v>
                 </c:pt>
@@ -5339,6 +5348,9 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>198359.00077810945</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>191259.80680937381</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5381,7 +5393,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -5600,6 +5612,9 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5609,7 +5624,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5828,6 +5843,9 @@
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>52359.000778109446</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>43259.806809373811</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5849,11 +5867,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="329935488"/>
-        <c:axId val="346255744"/>
+        <c:axId val="393928064"/>
+        <c:axId val="395000832"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="329935488"/>
+        <c:axId val="393928064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5896,14 +5914,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="346255744"/>
+        <c:crossAx val="395000832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="346255744"/>
+        <c:axId val="395000832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5954,7 +5972,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="329935488"/>
+        <c:crossAx val="393928064"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6360,7 +6378,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB75"/>
+  <dimension ref="A1:AB76"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -8878,6 +8896,35 @@
       </c>
       <c r="I75" s="17">
         <v>52359.000778109446</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="12.75">
+      <c r="A76" s="14">
+        <v>46112</v>
+      </c>
+      <c r="B76" s="15">
+        <v>4.8851591796875002</v>
+      </c>
+      <c r="C76" s="16">
+        <v>2000</v>
+      </c>
+      <c r="D76" s="17">
+        <v>409.40324080247029</v>
+      </c>
+      <c r="E76" s="17">
+        <v>39151.192371506011</v>
+      </c>
+      <c r="F76" s="17">
+        <v>191259.80680937381</v>
+      </c>
+      <c r="G76" s="17">
+        <v>148000</v>
+      </c>
+      <c r="H76" s="17">
+        <v>191259.80680937381</v>
+      </c>
+      <c r="I76" s="17">
+        <v>43259.806809373811</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="975">
   <si>
     <t>PE</t>
   </si>
@@ -3831,6 +3831,82 @@
   </si>
   <si>
     <t xml:space="preserve">2026/3/27
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/1
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/2
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/3
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/7
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/8
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/9
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/10
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/13
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/14
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/15
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/16
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/17
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/20
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/21
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/22
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/24
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/27
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/28
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/23
 </t>
   </si>
 </sst>
@@ -5867,11 +5943,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="393928064"/>
-        <c:axId val="395000832"/>
+        <c:axId val="588371840"/>
+        <c:axId val="588378496"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="393928064"/>
+        <c:axId val="588371840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5914,14 +5990,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="395000832"/>
+        <c:crossAx val="588378496"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="395000832"/>
+        <c:axId val="588378496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5972,7 +6048,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="393928064"/>
+        <c:crossAx val="588371840"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8940,7 +9016,7 @@
   <sheetPr codeName="Sheet4">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1210"/>
+  <dimension ref="A1:D1230"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="18"/>
@@ -27031,7 +27107,7 @@
     </row>
     <row r="1132" spans="1:4">
       <c r="A1132" s="18">
-        <f t="shared" ref="A1132:A1210" si="7">A1131+1</f>
+        <f t="shared" ref="A1132:A1226" si="7">A1131+1</f>
         <v>1130</v>
       </c>
       <c r="B1132" s="30">
@@ -28291,6 +28367,326 @@
       <c r="D1210" s="18">
         <f>SUM(C$3:C1210)/A1210</f>
         <v>26.136981933917117</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:4">
+      <c r="A1211" s="18">
+        <f t="shared" si="7"/>
+        <v>1209</v>
+      </c>
+      <c r="B1211" s="30" t="s">
+        <v>956</v>
+      </c>
+      <c r="C1211" s="31">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D1211" s="18">
+        <f>SUM(C$3:C1211)/A1211</f>
+        <v>26.140632072300974</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:4">
+      <c r="A1212" s="18">
+        <f t="shared" si="7"/>
+        <v>1210</v>
+      </c>
+      <c r="B1212" s="30" t="s">
+        <v>957</v>
+      </c>
+      <c r="C1212" s="31">
+        <v>30.340000150000002</v>
+      </c>
+      <c r="D1212" s="18">
+        <f>SUM(C$3:C1212)/A1212</f>
+        <v>26.144102624431305</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:4">
+      <c r="A1213" s="18">
+        <f t="shared" si="7"/>
+        <v>1211</v>
+      </c>
+      <c r="B1213" s="30" t="s">
+        <v>958</v>
+      </c>
+      <c r="C1213" s="31">
+        <v>29.940000529999999</v>
+      </c>
+      <c r="D1213" s="18">
+        <f>SUM(C$3:C1213)/A1213</f>
+        <v>26.147237139629958</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:4">
+      <c r="A1214" s="18">
+        <f t="shared" si="7"/>
+        <v>1212</v>
+      </c>
+      <c r="B1214" s="30" t="s">
+        <v>959</v>
+      </c>
+      <c r="C1214" s="31">
+        <v>29.979999540000001</v>
+      </c>
+      <c r="D1214" s="18">
+        <f>SUM(C$3:C1214)/A1214</f>
+        <v>26.150399484844783</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:4">
+      <c r="A1215" s="18">
+        <f t="shared" si="7"/>
+        <v>1213</v>
+      </c>
+      <c r="B1215" s="30" t="s">
+        <v>960</v>
+      </c>
+      <c r="C1215" s="31">
+        <v>31.379999160000001</v>
+      </c>
+      <c r="D1215" s="18">
+        <f>SUM(C$3:C1215)/A1215</f>
+        <v>26.154710778888603</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:4">
+      <c r="A1216" s="18">
+        <f t="shared" si="7"/>
+        <v>1214</v>
+      </c>
+      <c r="B1216" s="30" t="s">
+        <v>961</v>
+      </c>
+      <c r="C1216" s="31">
+        <v>31.299999239999998</v>
+      </c>
+      <c r="D1216" s="18">
+        <f>SUM(C$3:C1216)/A1216</f>
+        <v>26.158949072513902</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:4">
+      <c r="A1217" s="18">
+        <f t="shared" si="7"/>
+        <v>1215</v>
+      </c>
+      <c r="B1217" s="30" t="s">
+        <v>962</v>
+      </c>
+      <c r="C1217" s="31">
+        <v>32.38999939</v>
+      </c>
+      <c r="D1217" s="18">
+        <f>SUM(C$3:C1217)/A1217</f>
+        <v>26.164077508989202</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:4">
+      <c r="A1218" s="18">
+        <f t="shared" si="7"/>
+        <v>1216</v>
+      </c>
+      <c r="B1218" s="30" t="s">
+        <v>963</v>
+      </c>
+      <c r="C1218" s="31">
+        <v>32.72000122</v>
+      </c>
+      <c r="D1218" s="18">
+        <f>SUM(C$3:C1218)/A1218</f>
+        <v>26.169468893619968</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:4">
+      <c r="A1219" s="18">
+        <f t="shared" si="7"/>
+        <v>1217</v>
+      </c>
+      <c r="B1219" s="30" t="s">
+        <v>964</v>
+      </c>
+      <c r="C1219" s="31">
+        <v>33.349998470000003</v>
+      </c>
+      <c r="D1219" s="18">
+        <f>SUM(C$3:C1219)/A1219</f>
+        <v>26.175369082261199</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:4">
+      <c r="A1220" s="18">
+        <f t="shared" si="7"/>
+        <v>1218</v>
+      </c>
+      <c r="B1220" s="30" t="s">
+        <v>965</v>
+      </c>
+      <c r="C1220" s="31">
+        <v>33.060001370000002</v>
+      </c>
+      <c r="D1220" s="18">
+        <f>SUM(C$3:C1220)/A1220</f>
+        <v>26.181021489722394</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:4">
+      <c r="A1221" s="18">
+        <f t="shared" si="7"/>
+        <v>1219</v>
+      </c>
+      <c r="B1221" s="30" t="s">
+        <v>966</v>
+      </c>
+      <c r="C1221" s="31">
+        <v>33.799999239999998</v>
+      </c>
+      <c r="D1221" s="18">
+        <f>SUM(C$3:C1221)/A1221</f>
+        <v>26.187271676556094</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:4">
+      <c r="A1222" s="18">
+        <f t="shared" si="7"/>
+        <v>1220</v>
+      </c>
+      <c r="B1222" s="30" t="s">
+        <v>967</v>
+      </c>
+      <c r="C1222" s="31">
+        <v>33.91999817</v>
+      </c>
+      <c r="D1222" s="18">
+        <f>SUM(C$3:C1222)/A1222</f>
+        <v>26.193609976960555</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:4">
+      <c r="A1223" s="18">
+        <f t="shared" si="7"/>
+        <v>1221</v>
+      </c>
+      <c r="B1223" s="30" t="s">
+        <v>968</v>
+      </c>
+      <c r="C1223" s="31">
+        <v>34.040000919999997</v>
+      </c>
+      <c r="D1223" s="18">
+        <f>SUM(C$3:C1223)/A1223</f>
+        <v>26.200036177569103</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:4">
+      <c r="A1224" s="18">
+        <f t="shared" si="7"/>
+        <v>1222</v>
+      </c>
+      <c r="B1224" s="30" t="s">
+        <v>969</v>
+      </c>
+      <c r="C1224" s="31">
+        <v>34.159999849999998</v>
+      </c>
+      <c r="D1224" s="18">
+        <f>SUM(C$3:C1224)/A1224</f>
+        <v>26.206550059461435</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:4">
+      <c r="A1225" s="18">
+        <f t="shared" si="7"/>
+        <v>1223</v>
+      </c>
+      <c r="B1225" s="30" t="s">
+        <v>970</v>
+      </c>
+      <c r="C1225" s="31">
+        <v>34.380001069999999</v>
+      </c>
+      <c r="D1225" s="18">
+        <f>SUM(C$3:C1225)/A1225</f>
+        <v>26.213233175577983</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:4">
+      <c r="A1226" s="18">
+        <f t="shared" si="7"/>
+        <v>1224</v>
+      </c>
+      <c r="B1226" s="30" t="s">
+        <v>974</v>
+      </c>
+      <c r="C1226" s="31">
+        <v>34.32</v>
+      </c>
+      <c r="D1226" s="18">
+        <f>SUM(C$3:C1226)/A1226</f>
+        <v>26.219856351088133</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:4">
+      <c r="A1227" s="18">
+        <f t="shared" ref="A1227:A1230" si="8">A1226+1</f>
+        <v>1225</v>
+      </c>
+      <c r="B1227" s="30" t="s">
+        <v>971</v>
+      </c>
+      <c r="C1227" s="31">
+        <v>34.25</v>
+      </c>
+      <c r="D1227" s="18">
+        <f>SUM(C$3:C1227)/A1227</f>
+        <v>26.226411570393367</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:4">
+      <c r="A1228" s="18">
+        <f t="shared" si="8"/>
+        <v>1226</v>
+      </c>
+      <c r="B1228" s="30" t="s">
+        <v>972</v>
+      </c>
+      <c r="C1228" s="31">
+        <v>34.270000459999999</v>
+      </c>
+      <c r="D1228" s="18">
+        <f>SUM(C$3:C1228)/A1228</f>
+        <v>26.232972409618167</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:4">
+      <c r="A1229" s="18">
+        <f t="shared" si="8"/>
+        <v>1227</v>
+      </c>
+      <c r="B1229" s="30" t="s">
+        <v>973</v>
+      </c>
+      <c r="C1229" s="31">
+        <v>33.75</v>
+      </c>
+      <c r="D1229" s="18">
+        <f>SUM(C$3:C1229)/A1229</f>
+        <v>26.239098756472597</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:4">
+      <c r="A1230" s="18">
+        <f t="shared" si="8"/>
+        <v>1228</v>
+      </c>
+      <c r="B1230" s="30">
+        <v>46141</v>
+      </c>
+      <c r="C1230" s="31">
+        <v>34.459999080000003</v>
+      </c>
+      <c r="D1230" s="18">
+        <f>SUM(C$3:C1230)/A1230</f>
+        <v>26.245793300709998</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="956">
   <si>
     <t>PE</t>
   </si>
@@ -3831,82 +3831,6 @@
   </si>
   <si>
     <t xml:space="preserve">2026/3/27
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/4/1
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/4/2
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/4/3
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/4/7
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/4/8
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/4/9
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/4/10
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/4/13
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/4/14
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/4/15
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/4/16
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/4/17
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/4/20
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/4/21
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/4/22
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/4/24
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/4/27
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/4/28
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/4/23
 </t>
   </si>
 </sst>
@@ -5943,11 +5867,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="588371840"/>
-        <c:axId val="588378496"/>
+        <c:axId val="393928064"/>
+        <c:axId val="395000832"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="588371840"/>
+        <c:axId val="393928064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5990,14 +5914,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="588378496"/>
+        <c:crossAx val="395000832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="588378496"/>
+        <c:axId val="395000832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6048,7 +5972,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="588371840"/>
+        <c:crossAx val="393928064"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9016,7 +8940,7 @@
   <sheetPr codeName="Sheet4">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1230"/>
+  <dimension ref="A1:D1210"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="18"/>
@@ -27107,7 +27031,7 @@
     </row>
     <row r="1132" spans="1:4">
       <c r="A1132" s="18">
-        <f t="shared" ref="A1132:A1226" si="7">A1131+1</f>
+        <f t="shared" ref="A1132:A1210" si="7">A1131+1</f>
         <v>1130</v>
       </c>
       <c r="B1132" s="30">
@@ -28367,326 +28291,6 @@
       <c r="D1210" s="18">
         <f>SUM(C$3:C1210)/A1210</f>
         <v>26.136981933917117</v>
-      </c>
-    </row>
-    <row r="1211" spans="1:4">
-      <c r="A1211" s="18">
-        <f t="shared" si="7"/>
-        <v>1209</v>
-      </c>
-      <c r="B1211" s="30" t="s">
-        <v>956</v>
-      </c>
-      <c r="C1211" s="31">
-        <v>30.549999239999998</v>
-      </c>
-      <c r="D1211" s="18">
-        <f>SUM(C$3:C1211)/A1211</f>
-        <v>26.140632072300974</v>
-      </c>
-    </row>
-    <row r="1212" spans="1:4">
-      <c r="A1212" s="18">
-        <f t="shared" si="7"/>
-        <v>1210</v>
-      </c>
-      <c r="B1212" s="30" t="s">
-        <v>957</v>
-      </c>
-      <c r="C1212" s="31">
-        <v>30.340000150000002</v>
-      </c>
-      <c r="D1212" s="18">
-        <f>SUM(C$3:C1212)/A1212</f>
-        <v>26.144102624431305</v>
-      </c>
-    </row>
-    <row r="1213" spans="1:4">
-      <c r="A1213" s="18">
-        <f t="shared" si="7"/>
-        <v>1211</v>
-      </c>
-      <c r="B1213" s="30" t="s">
-        <v>958</v>
-      </c>
-      <c r="C1213" s="31">
-        <v>29.940000529999999</v>
-      </c>
-      <c r="D1213" s="18">
-        <f>SUM(C$3:C1213)/A1213</f>
-        <v>26.147237139629958</v>
-      </c>
-    </row>
-    <row r="1214" spans="1:4">
-      <c r="A1214" s="18">
-        <f t="shared" si="7"/>
-        <v>1212</v>
-      </c>
-      <c r="B1214" s="30" t="s">
-        <v>959</v>
-      </c>
-      <c r="C1214" s="31">
-        <v>29.979999540000001</v>
-      </c>
-      <c r="D1214" s="18">
-        <f>SUM(C$3:C1214)/A1214</f>
-        <v>26.150399484844783</v>
-      </c>
-    </row>
-    <row r="1215" spans="1:4">
-      <c r="A1215" s="18">
-        <f t="shared" si="7"/>
-        <v>1213</v>
-      </c>
-      <c r="B1215" s="30" t="s">
-        <v>960</v>
-      </c>
-      <c r="C1215" s="31">
-        <v>31.379999160000001</v>
-      </c>
-      <c r="D1215" s="18">
-        <f>SUM(C$3:C1215)/A1215</f>
-        <v>26.154710778888603</v>
-      </c>
-    </row>
-    <row r="1216" spans="1:4">
-      <c r="A1216" s="18">
-        <f t="shared" si="7"/>
-        <v>1214</v>
-      </c>
-      <c r="B1216" s="30" t="s">
-        <v>961</v>
-      </c>
-      <c r="C1216" s="31">
-        <v>31.299999239999998</v>
-      </c>
-      <c r="D1216" s="18">
-        <f>SUM(C$3:C1216)/A1216</f>
-        <v>26.158949072513902</v>
-      </c>
-    </row>
-    <row r="1217" spans="1:4">
-      <c r="A1217" s="18">
-        <f t="shared" si="7"/>
-        <v>1215</v>
-      </c>
-      <c r="B1217" s="30" t="s">
-        <v>962</v>
-      </c>
-      <c r="C1217" s="31">
-        <v>32.38999939</v>
-      </c>
-      <c r="D1217" s="18">
-        <f>SUM(C$3:C1217)/A1217</f>
-        <v>26.164077508989202</v>
-      </c>
-    </row>
-    <row r="1218" spans="1:4">
-      <c r="A1218" s="18">
-        <f t="shared" si="7"/>
-        <v>1216</v>
-      </c>
-      <c r="B1218" s="30" t="s">
-        <v>963</v>
-      </c>
-      <c r="C1218" s="31">
-        <v>32.72000122</v>
-      </c>
-      <c r="D1218" s="18">
-        <f>SUM(C$3:C1218)/A1218</f>
-        <v>26.169468893619968</v>
-      </c>
-    </row>
-    <row r="1219" spans="1:4">
-      <c r="A1219" s="18">
-        <f t="shared" si="7"/>
-        <v>1217</v>
-      </c>
-      <c r="B1219" s="30" t="s">
-        <v>964</v>
-      </c>
-      <c r="C1219" s="31">
-        <v>33.349998470000003</v>
-      </c>
-      <c r="D1219" s="18">
-        <f>SUM(C$3:C1219)/A1219</f>
-        <v>26.175369082261199</v>
-      </c>
-    </row>
-    <row r="1220" spans="1:4">
-      <c r="A1220" s="18">
-        <f t="shared" si="7"/>
-        <v>1218</v>
-      </c>
-      <c r="B1220" s="30" t="s">
-        <v>965</v>
-      </c>
-      <c r="C1220" s="31">
-        <v>33.060001370000002</v>
-      </c>
-      <c r="D1220" s="18">
-        <f>SUM(C$3:C1220)/A1220</f>
-        <v>26.181021489722394</v>
-      </c>
-    </row>
-    <row r="1221" spans="1:4">
-      <c r="A1221" s="18">
-        <f t="shared" si="7"/>
-        <v>1219</v>
-      </c>
-      <c r="B1221" s="30" t="s">
-        <v>966</v>
-      </c>
-      <c r="C1221" s="31">
-        <v>33.799999239999998</v>
-      </c>
-      <c r="D1221" s="18">
-        <f>SUM(C$3:C1221)/A1221</f>
-        <v>26.187271676556094</v>
-      </c>
-    </row>
-    <row r="1222" spans="1:4">
-      <c r="A1222" s="18">
-        <f t="shared" si="7"/>
-        <v>1220</v>
-      </c>
-      <c r="B1222" s="30" t="s">
-        <v>967</v>
-      </c>
-      <c r="C1222" s="31">
-        <v>33.91999817</v>
-      </c>
-      <c r="D1222" s="18">
-        <f>SUM(C$3:C1222)/A1222</f>
-        <v>26.193609976960555</v>
-      </c>
-    </row>
-    <row r="1223" spans="1:4">
-      <c r="A1223" s="18">
-        <f t="shared" si="7"/>
-        <v>1221</v>
-      </c>
-      <c r="B1223" s="30" t="s">
-        <v>968</v>
-      </c>
-      <c r="C1223" s="31">
-        <v>34.040000919999997</v>
-      </c>
-      <c r="D1223" s="18">
-        <f>SUM(C$3:C1223)/A1223</f>
-        <v>26.200036177569103</v>
-      </c>
-    </row>
-    <row r="1224" spans="1:4">
-      <c r="A1224" s="18">
-        <f t="shared" si="7"/>
-        <v>1222</v>
-      </c>
-      <c r="B1224" s="30" t="s">
-        <v>969</v>
-      </c>
-      <c r="C1224" s="31">
-        <v>34.159999849999998</v>
-      </c>
-      <c r="D1224" s="18">
-        <f>SUM(C$3:C1224)/A1224</f>
-        <v>26.206550059461435</v>
-      </c>
-    </row>
-    <row r="1225" spans="1:4">
-      <c r="A1225" s="18">
-        <f t="shared" si="7"/>
-        <v>1223</v>
-      </c>
-      <c r="B1225" s="30" t="s">
-        <v>970</v>
-      </c>
-      <c r="C1225" s="31">
-        <v>34.380001069999999</v>
-      </c>
-      <c r="D1225" s="18">
-        <f>SUM(C$3:C1225)/A1225</f>
-        <v>26.213233175577983</v>
-      </c>
-    </row>
-    <row r="1226" spans="1:4">
-      <c r="A1226" s="18">
-        <f t="shared" si="7"/>
-        <v>1224</v>
-      </c>
-      <c r="B1226" s="30" t="s">
-        <v>974</v>
-      </c>
-      <c r="C1226" s="31">
-        <v>34.32</v>
-      </c>
-      <c r="D1226" s="18">
-        <f>SUM(C$3:C1226)/A1226</f>
-        <v>26.219856351088133</v>
-      </c>
-    </row>
-    <row r="1227" spans="1:4">
-      <c r="A1227" s="18">
-        <f t="shared" ref="A1227:A1230" si="8">A1226+1</f>
-        <v>1225</v>
-      </c>
-      <c r="B1227" s="30" t="s">
-        <v>971</v>
-      </c>
-      <c r="C1227" s="31">
-        <v>34.25</v>
-      </c>
-      <c r="D1227" s="18">
-        <f>SUM(C$3:C1227)/A1227</f>
-        <v>26.226411570393367</v>
-      </c>
-    </row>
-    <row r="1228" spans="1:4">
-      <c r="A1228" s="18">
-        <f t="shared" si="8"/>
-        <v>1226</v>
-      </c>
-      <c r="B1228" s="30" t="s">
-        <v>972</v>
-      </c>
-      <c r="C1228" s="31">
-        <v>34.270000459999999</v>
-      </c>
-      <c r="D1228" s="18">
-        <f>SUM(C$3:C1228)/A1228</f>
-        <v>26.232972409618167</v>
-      </c>
-    </row>
-    <row r="1229" spans="1:4">
-      <c r="A1229" s="18">
-        <f t="shared" si="8"/>
-        <v>1227</v>
-      </c>
-      <c r="B1229" s="30" t="s">
-        <v>973</v>
-      </c>
-      <c r="C1229" s="31">
-        <v>33.75</v>
-      </c>
-      <c r="D1229" s="18">
-        <f>SUM(C$3:C1229)/A1229</f>
-        <v>26.239098756472597</v>
-      </c>
-    </row>
-    <row r="1230" spans="1:4">
-      <c r="A1230" s="18">
-        <f t="shared" si="8"/>
-        <v>1228</v>
-      </c>
-      <c r="B1230" s="30">
-        <v>46141</v>
-      </c>
-      <c r="C1230" s="31">
-        <v>34.459999080000003</v>
-      </c>
-      <c r="D1230" s="18">
-        <f>SUM(C$3:C1230)/A1230</f>
-        <v>26.245793300709998</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
@@ -5943,11 +5943,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="588371840"/>
-        <c:axId val="588378496"/>
+        <c:axId val="465683968"/>
+        <c:axId val="465685504"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="588371840"/>
+        <c:axId val="465683968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5990,14 +5990,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="588378496"/>
+        <c:crossAx val="465685504"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="588378496"/>
+        <c:axId val="465685504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6048,7 +6048,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="588371840"/>
+        <c:crossAx val="465683968"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9016,7 +9016,7 @@
   <sheetPr codeName="Sheet4">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1230"/>
+  <dimension ref="A1:D1231"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="18"/>
@@ -28627,7 +28627,7 @@
     </row>
     <row r="1227" spans="1:4">
       <c r="A1227" s="18">
-        <f t="shared" ref="A1227:A1230" si="8">A1226+1</f>
+        <f t="shared" ref="A1227:A1231" si="8">A1226+1</f>
         <v>1225</v>
       </c>
       <c r="B1227" s="30" t="s">
@@ -28687,6 +28687,22 @@
       <c r="D1230" s="18">
         <f>SUM(C$3:C1230)/A1230</f>
         <v>26.245793300709998</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:4">
+      <c r="A1231" s="18">
+        <f t="shared" si="8"/>
+        <v>1229</v>
+      </c>
+      <c r="B1231" s="30">
+        <v>46142</v>
+      </c>
+      <c r="C1231" s="31">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D1231" s="18">
+        <f>SUM(C$3:C1231)/A1231</f>
+        <v>26.252550181051159</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
@@ -4479,7 +4479,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -4701,6 +4701,9 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4710,7 +4713,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4932,6 +4935,9 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>148000</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>150000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4974,7 +4980,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -5196,6 +5202,9 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5205,7 +5214,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>2000.0000000000002</c:v>
                 </c:pt>
@@ -5427,6 +5436,9 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>191259.80680937381</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>219124.99999266435</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5469,7 +5481,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -5691,6 +5703,9 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5700,7 +5715,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5922,6 +5937,9 @@
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>43259.806809373811</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>69124.99999266435</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5943,11 +5961,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="465683968"/>
-        <c:axId val="465685504"/>
+        <c:axId val="89256704"/>
+        <c:axId val="383926272"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="465683968"/>
+        <c:axId val="89256704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5990,14 +6008,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="465685504"/>
+        <c:crossAx val="383926272"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="465685504"/>
+        <c:axId val="383926272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6048,7 +6066,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="465683968"/>
+        <c:crossAx val="89256704"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6454,7 +6472,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB76"/>
+  <dimension ref="A1:AB77"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -9001,6 +9019,35 @@
       </c>
       <c r="I76" s="17">
         <v>43259.806809373811</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="12.75">
+      <c r="A77" s="14">
+        <v>46142</v>
+      </c>
+      <c r="B77" s="15">
+        <v>5.5458081054687502</v>
+      </c>
+      <c r="C77" s="16">
+        <v>2000</v>
+      </c>
+      <c r="D77" s="17">
+        <v>360.63274494257917</v>
+      </c>
+      <c r="E77" s="17">
+        <v>39511.825116448592</v>
+      </c>
+      <c r="F77" s="17">
+        <v>219124.99999266435</v>
+      </c>
+      <c r="G77" s="17">
+        <v>150000</v>
+      </c>
+      <c r="H77" s="17">
+        <v>219124.99999266435</v>
+      </c>
+      <c r="I77" s="17">
+        <v>69124.99999266435</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel1prac.xlsx
@@ -4543,7 +4543,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -4768,6 +4768,9 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4777,7 +4780,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5002,6 +5005,9 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>150000</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>152000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5044,7 +5050,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -5269,6 +5275,9 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5278,7 +5287,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>2000.0000000000002</c:v>
                 </c:pt>
@@ -5503,6 +5512,9 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>219124.99999266435</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>237913.37769723308</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5545,7 +5557,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>43889</c:v>
                 </c:pt>
@@ -5770,6 +5782,9 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5779,7 +5794,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6004,6 +6019,9 @@
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>69124.99999266435</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>85913.377697233082</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6025,11 +6043,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="162922880"/>
-        <c:axId val="162924800"/>
+        <c:axId val="99720192"/>
+        <c:axId val="103724160"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="162922880"/>
+        <c:axId val="99720192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6072,14 +6090,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="162924800"/>
+        <c:crossAx val="103724160"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="162924800"/>
+        <c:axId val="103724160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6130,7 +6148,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="162922880"/>
+        <c:crossAx val="99720192"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6536,7 +6554,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB77"/>
+  <dimension ref="A1:AB78"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -9112,6 +9130,35 @@
       </c>
       <c r="I77" s="17">
         <v>69124.99999266435</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="12.75">
+      <c r="A78" s="14">
+        <v>46171</v>
+      </c>
+      <c r="B78" s="15">
+        <v>5.970703125</v>
+      </c>
+      <c r="C78" s="16">
+        <v>2000</v>
+      </c>
+      <c r="D78" s="17">
+        <v>334.9689237814851</v>
+      </c>
+      <c r="E78" s="17">
+        <v>39846.794040230074</v>
+      </c>
+      <c r="F78" s="17">
+        <v>237913.37769723308</v>
+      </c>
+      <c r="G78" s="17">
+        <v>152000</v>
+      </c>
+      <c r="H78" s="17">
+        <v>237913.37769723308</v>
+      </c>
+      <c r="I78" s="17">
+        <v>85913.377697233082</v>
       </c>
     </row>
   </sheetData>
